--- a/05_算法与标定/温度阻值标定.xlsx
+++ b/05_算法与标定/温度阻值标定.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18580" windowHeight="9880"/>
+    <workbookView windowWidth="24750" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="20">
   <si>
     <t>阻值</t>
   </si>
@@ -74,17 +74,33 @@
   </si>
   <si>
     <t>平均误差</t>
+  </si>
+  <si>
+    <t>精密电阻板V2</t>
+  </si>
+  <si>
+    <t>温度T</t>
+  </si>
+  <si>
+    <t>并联3.9k</t>
+  </si>
+  <si>
+    <t>并5.1k</t>
+  </si>
+  <si>
+    <t>并联2.7k</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="0.00_ "/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -789,7 +805,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -821,6 +837,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1134,10 +1153,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
-    <col min="3" max="5" width="11.7272727272727"/>
+    <col min="3" max="3" width="11.7272727272727"/>
+    <col min="4" max="4" width="13.3454545454545" customWidth="1"/>
+    <col min="5" max="5" width="11.7272727272727"/>
     <col min="6" max="7" width="12.8181818181818"/>
   </cols>
   <sheetData>
@@ -1355,7 +1376,6 @@
       <c r="A18" s="1">
         <v>0</v>
       </c>
-      <c r="B18"/>
       <c r="C18" s="2"/>
       <c r="D18" s="1"/>
       <c r="E18" s="2"/>
@@ -1662,6 +1682,152 @@
         <f>AVERAGE(G19:G29)</f>
         <v>0.567895454545455</v>
       </c>
+    </row>
+    <row r="32" ht="14.75"/>
+    <row r="33" spans="1:5">
+      <c r="D33" t="s">
+        <v>15</v>
+      </c>
+      <c r="E33" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="1">
+        <v>81.76</v>
+      </c>
+      <c r="B34">
+        <v>80.6</v>
+      </c>
+      <c r="C34" t="s">
+        <v>17</v>
+      </c>
+      <c r="D34">
+        <v>80.49</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="2">
+        <v>82.4</v>
+      </c>
+      <c r="B35">
+        <v>82</v>
+      </c>
+      <c r="D35">
+        <v>82.42</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="2">
+        <v>100.1</v>
+      </c>
+      <c r="B36">
+        <v>100</v>
+      </c>
+      <c r="D36">
+        <v>100.17</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="2">
+        <v>110.1</v>
+      </c>
+      <c r="B37">
+        <v>107</v>
+      </c>
+      <c r="C37" t="s">
+        <v>18</v>
+      </c>
+      <c r="D37">
+        <v>107.72</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="2">
+        <v>112.6</v>
+      </c>
+      <c r="B38">
+        <v>113</v>
+      </c>
+      <c r="C38"/>
+      <c r="D38" s="11">
+        <v>112.6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="1">
+        <v>120.4</v>
+      </c>
+      <c r="B39">
+        <v>115</v>
+      </c>
+      <c r="C39" t="s">
+        <v>19</v>
+      </c>
+      <c r="D39">
+        <v>115.28</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="2">
+        <v>122.9</v>
+      </c>
+      <c r="B40">
+        <v>123</v>
+      </c>
+      <c r="D40">
+        <v>122.86</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="2">
+        <v>130.9</v>
+      </c>
+      <c r="B41">
+        <v>130</v>
+      </c>
+      <c r="D41">
+        <v>130.81</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="2">
+        <v>138.85</v>
+      </c>
+      <c r="B42">
+        <v>138</v>
+      </c>
+      <c r="D42">
+        <v>138.74</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="2">
+        <v>150.2</v>
+      </c>
+      <c r="B43">
+        <v>150</v>
+      </c>
+      <c r="D43">
+        <v>150.05</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="1">
+        <v>160.15</v>
+      </c>
+      <c r="B44">
+        <v>154</v>
+      </c>
+      <c r="C44" t="s">
+        <v>17</v>
+      </c>
+      <c r="D44" s="11">
+        <v>153.9</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
